--- a/master/result/14_总裁偏爱：独家宠爱/14_总裁的偏爱.xlsx
+++ b/master/result/14_总裁偏爱：独家宠爱/14_总裁的偏爱.xlsx
@@ -397,599 +397,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:D53"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>garbage</v>
       </c>
       <c r="B2" t="str">
-        <v>garbage</v>
+        <v>/garbage/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>垃圾</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>weekday</v>
       </c>
       <c r="B3" t="str">
-        <v>weekday</v>
+        <v>/weekday/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>工作日</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>tedious</v>
       </c>
       <c r="B4" t="str">
-        <v>tedious</v>
+        <v>/tedious/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>乏味</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>meeting</v>
       </c>
       <c r="B5" t="str">
-        <v>meeting</v>
+        <v>/meeting/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>会议</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>organ</v>
       </c>
       <c r="B6" t="str">
-        <v>organ</v>
+        <v>/organ/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>器官</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>hypothesis</v>
       </c>
       <c r="B7" t="str">
-        <v>hypothesis</v>
+        <v>/hypothesis/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>假设</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>spot</v>
       </c>
       <c r="B8" t="str">
-        <v>spot</v>
+        <v>/spɒt/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>地点</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>track</v>
       </c>
       <c r="B9" t="str">
-        <v>track</v>
+        <v>/træk/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>轨迹</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>inference</v>
       </c>
       <c r="B10" t="str">
-        <v>inference</v>
+        <v>/inference/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>推论</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>advise</v>
       </c>
       <c r="B11" t="str">
-        <v>advise</v>
+        <v>/advise/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>建议</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>egg</v>
       </c>
       <c r="B12" t="str">
-        <v>egg</v>
+        <v>/egg/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>蛋</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>maid</v>
       </c>
       <c r="B13" t="str">
-        <v>maid</v>
+        <v>/maid/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>女仆</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>please</v>
       </c>
       <c r="B14" t="str">
-        <v>please</v>
+        <v>/please/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>请</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>harbor</v>
       </c>
       <c r="B15" t="str">
-        <v>harbor</v>
+        <v>/harbor/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>海港</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>load</v>
       </c>
       <c r="B16" t="str">
-        <v>load</v>
+        <v>/ləʊd/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>装载</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>gorgeous</v>
       </c>
       <c r="B17" t="str">
+        <v>/gorgeous/</v>
+      </c>
+      <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>灿烂</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>personnel</v>
+      </c>
+      <c r="B18" t="str">
+        <v>/personnel/</v>
+      </c>
+      <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>人事</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>uproar</v>
+      </c>
+      <c r="B19" t="str">
+        <v>/uproar/</v>
+      </c>
+      <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>骚动</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>lottery</v>
+      </c>
+      <c r="B20" t="str">
+        <v>/lottery/</v>
+      </c>
+      <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>彩票</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>complicate</v>
+      </c>
+      <c r="B21" t="str">
+        <v>/complicate/</v>
+      </c>
+      <c r="C21" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>复杂</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>accordingly</v>
+      </c>
+      <c r="B22" t="str">
+        <v>/accordingly/</v>
+      </c>
+      <c r="C22" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>相应地</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>muscle</v>
+      </c>
+      <c r="B23" t="str">
+        <v>/muscle/</v>
+      </c>
+      <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>肌肉</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>elder</v>
+      </c>
+      <c r="B24" t="str">
+        <v>/elder/</v>
+      </c>
+      <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>长者</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>child</v>
+      </c>
+      <c r="B25" t="str">
+        <v>/child/</v>
+      </c>
+      <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>孩子</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>alphabet</v>
+      </c>
+      <c r="B26" t="str">
+        <v>/alphabet/</v>
+      </c>
+      <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>字母</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>endow</v>
+      </c>
+      <c r="B27" t="str">
+        <v>/endow/</v>
+      </c>
+      <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>赋予</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>inhibit</v>
+      </c>
+      <c r="B28" t="str">
+        <v>/inhibit/</v>
+      </c>
+      <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>抑制</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>tour</v>
+      </c>
+      <c r="B29" t="str">
+        <v>/tʊə/</v>
+      </c>
+      <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>旅行</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>aircraft</v>
+      </c>
+      <c r="B30" t="str">
+        <v>/ˈeəkrɑːft/</v>
+      </c>
+      <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>飞机</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>rib</v>
+      </c>
+      <c r="B31" t="str">
+        <v>/rib/</v>
+      </c>
+      <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>肋骨</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>paralyze</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/paralyze/</v>
+      </c>
+      <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>瘫痪</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>contact</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/ˈkɒntækt/</v>
+      </c>
+      <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>联系</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>thing</v>
+      </c>
+      <c r="B34" t="str">
+        <v>/thing/</v>
+      </c>
+      <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>事情</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>oral</v>
+      </c>
+      <c r="B35" t="str">
+        <v>/oral/</v>
+      </c>
+      <c r="C35" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>口头的</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>poisonous</v>
+      </c>
+      <c r="B36" t="str">
+        <v>/poisonous/</v>
+      </c>
+      <c r="C36" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>恶意的</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>savage</v>
+      </c>
+      <c r="B37" t="str">
+        <v>/savage/</v>
+      </c>
+      <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>野蛮</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>bolt</v>
+      </c>
+      <c r="B38" t="str">
+        <v>/bolt/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>螺栓</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>detector</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/detector/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>侦查</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>unanimous</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/unanimous/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>一致</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>clockwise</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/clockwise/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>顺时针</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>sprout</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/sprout/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>发芽</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>visitor</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/visitor/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>访问</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
         <v>gorgeous</v>
       </c>
-      <c r="C17" t="str">
-        <v>灿烂</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>personnel</v>
-      </c>
-      <c r="C18" t="str">
-        <v>人事</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>uproar</v>
-      </c>
-      <c r="C19" t="str">
-        <v>骚动</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>lottery</v>
-      </c>
-      <c r="C20" t="str">
-        <v>彩票</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>complicate</v>
-      </c>
-      <c r="C21" t="str">
-        <v>复杂</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
-        <v>accordingly</v>
-      </c>
-      <c r="C22" t="str">
-        <v>相应地</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <v>muscle</v>
-      </c>
-      <c r="C23" t="str">
-        <v>肌肉</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v>elder</v>
-      </c>
-      <c r="C24" t="str">
-        <v>长者</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>child</v>
-      </c>
-      <c r="C25" t="str">
-        <v>孩子</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>alphabet</v>
-      </c>
-      <c r="C26" t="str">
-        <v>字母</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>endow</v>
-      </c>
-      <c r="C27" t="str">
-        <v>赋予</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>inhibit</v>
-      </c>
-      <c r="C28" t="str">
-        <v>抑制</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>tour</v>
-      </c>
-      <c r="C29" t="str">
-        <v>旅行</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>aircraft</v>
-      </c>
-      <c r="C30" t="str">
-        <v>飞机</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>rib</v>
-      </c>
-      <c r="C31" t="str">
-        <v>肋骨</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>paralyze</v>
-      </c>
-      <c r="C32" t="str">
-        <v>瘫痪</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>contact</v>
-      </c>
-      <c r="C33" t="str">
-        <v>联系</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>thing</v>
-      </c>
-      <c r="C34" t="str">
-        <v>事情</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>oral</v>
-      </c>
-      <c r="C35" t="str">
-        <v>口头的</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>poisonous</v>
-      </c>
-      <c r="C36" t="str">
-        <v>恶意的</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>savage</v>
-      </c>
-      <c r="C37" t="str">
-        <v>野蛮</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>bolt</v>
-      </c>
-      <c r="C38" t="str">
-        <v>螺栓</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>detector</v>
-      </c>
-      <c r="C39" t="str">
-        <v>侦查</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>unanimous</v>
-      </c>
-      <c r="C40" t="str">
-        <v>一致</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>clockwise</v>
-      </c>
-      <c r="C41" t="str">
-        <v>顺时针</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>sprout</v>
-      </c>
-      <c r="C42" t="str">
-        <v>发芽</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>visitor</v>
-      </c>
-      <c r="C43" t="str">
-        <v>访问</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
       <c r="B44" t="str">
+        <v>/gorgeous/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>华丽</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>cord</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/kɔːd/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>绳索</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>predominant</v>
+      </c>
+      <c r="B46" t="str">
+        <v>/predominant/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>占主导地位的</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>enthusiasm</v>
+      </c>
+      <c r="B47" t="str">
+        <v>/enthusiasm/</v>
+      </c>
+      <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>热情</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>peace</v>
+      </c>
+      <c r="B48" t="str">
+        <v>/peace/</v>
+      </c>
+      <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>安宁</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>shift</v>
+      </c>
+      <c r="B49" t="str">
+        <v>/ʃɪft/</v>
+      </c>
+      <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
+        <v>转换</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>fuel</v>
+      </c>
+      <c r="B50" t="str">
+        <v>/fuel/</v>
+      </c>
+      <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
+        <v>加燃料</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>undo</v>
+      </c>
+      <c r="B51" t="str">
+        <v>/ʌnˈduː/</v>
+      </c>
+      <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
+        <v>解开</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>hold</v>
+      </c>
+      <c r="B52" t="str">
+        <v>/həʊld/</v>
+      </c>
+      <c r="C52" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D52" t="str">
+        <v>握住</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
         <v>gorgeous</v>
       </c>
-      <c r="C44" t="str">
-        <v>华丽</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>cord</v>
-      </c>
-      <c r="C45" t="str">
-        <v>绳索</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>predominant</v>
-      </c>
-      <c r="C46" t="str">
-        <v>占主导地位的</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>enthusiasm</v>
-      </c>
-      <c r="C47" t="str">
-        <v>热情</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>peace</v>
-      </c>
-      <c r="C48" t="str">
-        <v>安宁</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>shift</v>
-      </c>
-      <c r="C49" t="str">
-        <v>转换</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>fuel</v>
-      </c>
-      <c r="C50" t="str">
-        <v>加燃料</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>undo</v>
-      </c>
-      <c r="C51" t="str">
-        <v>解开</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>hold</v>
-      </c>
-      <c r="C52" t="str">
-        <v>握住</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
       <c r="B53" t="str">
-        <v>gorgeous</v>
+        <v>/gorgeous/</v>
       </c>
       <c r="C53" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D53" t="str">
         <v>美丽</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>